--- a/Misc/RDBES/inputtable/annex23sc.xlsx
+++ b/Misc/RDBES/inputtable/annex23sc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\wg_WGEEL\Misc\RDBES\inputtable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{122A10C3-1946-4BEA-B618-EB4CC074A512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A5D984-F08E-4B67-BADD-37A8D57156B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="609">
   <si>
     <t>ser_cou_code</t>
   </si>
@@ -1451,6 +1451,402 @@
   </si>
   <si>
     <t>FDIA_SILVEREELINDEX_DENOEVERIJSSELMEER</t>
+  </si>
+  <si>
+    <t>KavlS</t>
+  </si>
+  <si>
+    <t>Kävlingeån</t>
+  </si>
+  <si>
+    <t>WyeY</t>
+  </si>
+  <si>
+    <t>Wye River</t>
+  </si>
+  <si>
+    <t>VilS</t>
+  </si>
+  <si>
+    <t>Vilaine Didson Silver eel survey</t>
+  </si>
+  <si>
+    <t>TesY</t>
+  </si>
+  <si>
+    <t>Test River</t>
+  </si>
+  <si>
+    <t>ParY</t>
+  </si>
+  <si>
+    <t>Parrett River</t>
+  </si>
+  <si>
+    <t>PlyY</t>
+  </si>
+  <si>
+    <t>Plym River</t>
+  </si>
+  <si>
+    <t>TamY</t>
+  </si>
+  <si>
+    <t>Tamar River</t>
+  </si>
+  <si>
+    <t>LespY</t>
+  </si>
+  <si>
+    <t>Laguna di Lesina</t>
+  </si>
+  <si>
+    <t>TawY</t>
+  </si>
+  <si>
+    <t>Taw River</t>
+  </si>
+  <si>
+    <t>TegY</t>
+  </si>
+  <si>
+    <t>Teign River</t>
+  </si>
+  <si>
+    <t>TyTY</t>
+  </si>
+  <si>
+    <t>Tywi</t>
+  </si>
+  <si>
+    <t>MonS</t>
+  </si>
+  <si>
+    <t>Mondego Silver</t>
+  </si>
+  <si>
+    <t>MiScG</t>
+  </si>
+  <si>
+    <t>Minho scientific monitoring</t>
+  </si>
+  <si>
+    <t>DaugY</t>
+  </si>
+  <si>
+    <t>LilY</t>
+  </si>
+  <si>
+    <t>EllY</t>
+  </si>
+  <si>
+    <t>Ellen River</t>
+  </si>
+  <si>
+    <t>ZeiS</t>
+  </si>
+  <si>
+    <t>Zeimena river</t>
+  </si>
+  <si>
+    <t>RieS</t>
+  </si>
+  <si>
+    <t>Riese river</t>
+  </si>
+  <si>
+    <t>TrasY</t>
+  </si>
+  <si>
+    <t>Lago Trasimeno</t>
+  </si>
+  <si>
+    <t>InagG</t>
+  </si>
+  <si>
+    <t>GotaY</t>
+  </si>
+  <si>
+    <t>Göta Älv  trapping all</t>
+  </si>
+  <si>
+    <t>PilaY</t>
+  </si>
+  <si>
+    <t>KerY</t>
+  </si>
+  <si>
+    <t>Kertuojai lake</t>
+  </si>
+  <si>
+    <t>TaivY</t>
+  </si>
+  <si>
+    <t>Taivassalo coast</t>
+  </si>
+  <si>
+    <t>VaakS</t>
+  </si>
+  <si>
+    <t>Vääksynjoki</t>
+  </si>
+  <si>
+    <t>KrolY</t>
+  </si>
+  <si>
+    <t>Kroku Lanka lake</t>
+  </si>
+  <si>
+    <t>VieY</t>
+  </si>
+  <si>
+    <t>Vievis lake</t>
+  </si>
+  <si>
+    <t>YerY</t>
+  </si>
+  <si>
+    <t>YerY electrofishing survey</t>
+  </si>
+  <si>
+    <t>WaSG</t>
+  </si>
+  <si>
+    <t>Warnow Scientific Glass eel monitoring</t>
+  </si>
+  <si>
+    <t>WaSEY</t>
+  </si>
+  <si>
+    <t>Warnow Scientific Elver monitoring</t>
+  </si>
+  <si>
+    <t>GR_WePe</t>
+  </si>
+  <si>
+    <t>KaloY</t>
+  </si>
+  <si>
+    <t>Kalogera_Yellow</t>
+  </si>
+  <si>
+    <t>KotY</t>
+  </si>
+  <si>
+    <t>Kotychi_Yellow</t>
+  </si>
+  <si>
+    <t>VeAmG</t>
+  </si>
+  <si>
+    <t>PolsY</t>
+  </si>
+  <si>
+    <t>SciY</t>
+  </si>
+  <si>
+    <t>Scie electrofishing survey</t>
+  </si>
+  <si>
+    <t>AustY</t>
+  </si>
+  <si>
+    <t>Austevoll fyke net survey</t>
+  </si>
+  <si>
+    <t>FremY</t>
+  </si>
+  <si>
+    <t>Fremur electrofishing survey</t>
+  </si>
+  <si>
+    <t>AdoY</t>
+  </si>
+  <si>
+    <t>Adour elecrofishing survey</t>
+  </si>
+  <si>
+    <t>GarY</t>
+  </si>
+  <si>
+    <t>Garonne electrofishing survey</t>
+  </si>
+  <si>
+    <t>SeNY</t>
+  </si>
+  <si>
+    <t>Sevre Niortaise electrofishing survey</t>
+  </si>
+  <si>
+    <t>TrasS</t>
+  </si>
+  <si>
+    <t>Lago Trasimeno near Torrente del Caina (north)</t>
+  </si>
+  <si>
+    <t>OrnY</t>
+  </si>
+  <si>
+    <t>Orne electrofishing survey</t>
+  </si>
+  <si>
+    <t>TouY</t>
+  </si>
+  <si>
+    <t>Touques electrofishing survey</t>
+  </si>
+  <si>
+    <t>VirY</t>
+  </si>
+  <si>
+    <t>VirY electrofishing survey</t>
+  </si>
+  <si>
+    <t>FreS</t>
+  </si>
+  <si>
+    <t>Frémur</t>
+  </si>
+  <si>
+    <t>SouY</t>
+  </si>
+  <si>
+    <t>Souston elecrofishing survey</t>
+  </si>
+  <si>
+    <t>BreY</t>
+  </si>
+  <si>
+    <t>Bresle electrofishing survey</t>
+  </si>
+  <si>
+    <t>SeiY</t>
+  </si>
+  <si>
+    <t>Seine electrofishing survey</t>
+  </si>
+  <si>
+    <t>PilaS</t>
+  </si>
+  <si>
+    <t>BRWS</t>
+  </si>
+  <si>
+    <t>FDIA_SILVEREELINDEX_BOVENRIJNWAAL</t>
+  </si>
+  <si>
+    <t>BE_Meus</t>
+  </si>
+  <si>
+    <t>MeusY</t>
+  </si>
+  <si>
+    <t>Meuse Lixhe dam trapping partial</t>
+  </si>
+  <si>
+    <t>MarY</t>
+  </si>
+  <si>
+    <t>FYMA_MARKERMEER</t>
+  </si>
+  <si>
+    <t>LeacG</t>
+  </si>
+  <si>
+    <t>GariG</t>
+  </si>
+  <si>
+    <t>OrbfG</t>
+  </si>
+  <si>
+    <t>SkaY</t>
+  </si>
+  <si>
+    <t>Skagerrak Beach Seine Survey</t>
+  </si>
+  <si>
+    <t>BalY</t>
+  </si>
+  <si>
+    <t>Balsys lake</t>
+  </si>
+  <si>
+    <t>KertS</t>
+  </si>
+  <si>
+    <t>river from Kertuojas lake</t>
+  </si>
+  <si>
+    <t>GariY</t>
+  </si>
+  <si>
+    <t>OrbfY</t>
+  </si>
+  <si>
+    <t>LeocY</t>
+  </si>
+  <si>
+    <t>LezaY</t>
+  </si>
+  <si>
+    <t>LescY</t>
+  </si>
+  <si>
+    <t>LereY</t>
+  </si>
+  <si>
+    <t>Laguna di Lesina Sacca Occidentale/ Sacca Orientale, Area Centrale</t>
+  </si>
+  <si>
+    <t>PogoY</t>
+  </si>
+  <si>
+    <t>TibdY</t>
+  </si>
+  <si>
+    <t>Tiber Dragoncello</t>
+  </si>
+  <si>
+    <t>PobeY</t>
+  </si>
+  <si>
+    <t>BrokGY</t>
+  </si>
+  <si>
+    <t>Broklandsau Pumping Station</t>
+  </si>
+  <si>
+    <t>LangGY</t>
+  </si>
+  <si>
+    <t>Langenhorn Pumping Station</t>
+  </si>
+  <si>
+    <t>WiFG</t>
+  </si>
+  <si>
+    <t>Frische Grube</t>
+  </si>
+  <si>
+    <t>OriY</t>
+  </si>
+  <si>
+    <t>Oria river basin</t>
+  </si>
+  <si>
+    <t>OriS</t>
+  </si>
+  <si>
+    <t>EmsBGY</t>
+  </si>
+  <si>
+    <t>Ems (Bollingerfaehr) Elver monitoring</t>
+  </si>
+  <si>
+    <t>DoElY</t>
+  </si>
+  <si>
+    <t>Dove Elde eel ladder</t>
   </si>
 </sst>
 </file>
@@ -1844,7 +2240,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -5264,6 +5660,1264 @@
         <v>9</v>
       </c>
     </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A217" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A219" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A221" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A235" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A236" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A237" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A238" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A239" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A240" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A241" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A243" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A244" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A245" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A246" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A247" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A248" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A249" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A250" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A251" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A252" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A253" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A254" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A255" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A256" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A257" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A258" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A259" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A260" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A261" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A262" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A263" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A264" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A265" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A266" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A267" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A268" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A269" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A270" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A271" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A272" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A273" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A274" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A275" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
